--- a/OrangeHRM/Workflow/OrangeHRM_LoginWorkFlow.xlsx
+++ b/OrangeHRM/Workflow/OrangeHRM_LoginWorkFlow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Life\Learning\Esprit\PFE\Project\TessanTIS\TessanTIS.OrangeHRM.Data.Impl\Workflow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Life\Learning\Esprit\PFE\Project\TessanTIS\OrangeHRM\Workflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F57688-4C67-4876-BCF6-B6FBC8260768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE05CE1-610E-462C-91DB-E80F9D9B62AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6540" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
+    <workbookView xWindow="28680" yWindow="-6540" windowWidth="29040" windowHeight="15720" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="OrangeHRM_Login_TC001" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="14">
   <si>
     <t>StepNumber</t>
   </si>
@@ -63,12 +63,6 @@
     <t>CreateAccountFirstStep</t>
   </si>
   <si>
-    <t>CreateAccountSecondStep</t>
-  </si>
-  <si>
-    <t>VerifyUserAccountCreatedSuccefuly</t>
-  </si>
-  <si>
     <t>VerifyErrorMessageForSignUpFirstStep</t>
   </si>
   <si>
@@ -76,6 +70,15 @@
   </si>
   <si>
     <t>VerifyErrorMessageForEmptyFields</t>
+  </si>
+  <si>
+    <t>OpenOrangeHRMWebSite</t>
+  </si>
+  <si>
+    <t>VerifyUserLoggedInSuccessfully</t>
+  </si>
+  <si>
+    <t>LoginWithCorrectCredential</t>
   </si>
 </sst>
 </file>
@@ -433,11 +436,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2223E30E-CC8E-4585-A018-9A29E0B468FB}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -462,7 +468,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -479,7 +485,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -496,7 +502,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -505,40 +511,6 @@
         <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -631,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -732,7 +704,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -749,7 +721,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -769,21 +741,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C1D9689BC10D74FBDB569E6E80ED286" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e193ee76a93e1a439b3cae51403dd597">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c494e978-fd52-4122-96f3-83d7c94282c9" xmlns:ns4="b9756793-60a6-4e91-b93f-ed15f553695a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f59eb8f914e4cb4e3fda9f0b6e41ab4" ns3:_="" ns4:_="">
     <xsd:import namespace="c494e978-fd52-4122-96f3-83d7c94282c9"/>
@@ -986,24 +943,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E949F8F-1265-4F7D-8B3B-442451397EE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA388CD-F2B6-42EB-8847-A12F80FD17BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1020,4 +975,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E949F8F-1265-4F7D-8B3B-442451397EE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/OrangeHRM/Workflow/OrangeHRM_LoginWorkFlow.xlsx
+++ b/OrangeHRM/Workflow/OrangeHRM_LoginWorkFlow.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Life\Learning\Esprit\PFE\Project\TessanTIS\OrangeHRM\Workflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE05CE1-610E-462C-91DB-E80F9D9B62AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5557E514-803B-488A-949E-3EE5D3CE2CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6540" windowWidth="29040" windowHeight="15720" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
+    <workbookView xWindow="28680" yWindow="-9105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="OrangeHRM_Login_TC001" sheetId="1" r:id="rId1"/>
     <sheet name="OrangeHRM_Login_TC002" sheetId="2" r:id="rId2"/>
-    <sheet name="OrangeHRM_Login_TC003" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>StepNumber</t>
   </si>
@@ -52,24 +51,6 @@
   </si>
   <si>
     <t>V1</t>
-  </si>
-  <si>
-    <t>OpenAutomationPracticeWebSite</t>
-  </si>
-  <si>
-    <t>AccessToLoginPage</t>
-  </si>
-  <si>
-    <t>CreateAccountFirstStep</t>
-  </si>
-  <si>
-    <t>VerifyErrorMessageForSignUpFirstStep</t>
-  </si>
-  <si>
-    <t>CreateAccountSecondStepWithEmptyFields</t>
-  </si>
-  <si>
-    <t>VerifyErrorMessageForEmptyFields</t>
   </si>
   <si>
     <t>OpenOrangeHRMWebSite</t>
@@ -468,7 +449,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -485,7 +466,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -502,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -523,224 +504,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049E3AE9-60A4-407C-BC4D-B3D2165874D7}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.26953125" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B86C05E-9ED9-4B06-9D2C-9D0DEF92076F}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C1D9689BC10D74FBDB569E6E80ED286" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e193ee76a93e1a439b3cae51403dd597">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c494e978-fd52-4122-96f3-83d7c94282c9" xmlns:ns4="b9756793-60a6-4e91-b93f-ed15f553695a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f59eb8f914e4cb4e3fda9f0b6e41ab4" ns3:_="" ns4:_="">
     <xsd:import namespace="c494e978-fd52-4122-96f3-83d7c94282c9"/>
@@ -943,22 +735,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E949F8F-1265-4F7D-8B3B-442451397EE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA388CD-F2B6-42EB-8847-A12F80FD17BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -975,21 +769,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E949F8F-1265-4F7D-8B3B-442451397EE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>